--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104651_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104651_W22.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4574</v>
+        <v>5.0879</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0211</v>
+        <v>4.0026</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4363</v>
+        <v>1.0853</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3602</v>
+        <v>2.0948</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9017</v>
+        <v>0.2702</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4585</v>
+        <v>1.8246</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0414</v>
+        <v>3.6822</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5412</v>
+        <v>0.4579</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5002</v>
+        <v>3.2243</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6812</v>
+        <v>-1.5874</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3605</v>
+        <v>-0.1877</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.0417</v>
+        <v>-1.3997</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5774</v>
+        <v>-0.7305</v>
       </c>
       <c r="T2" t="n">
-        <v>0.248</v>
+        <v>-0.4441</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3293</v>
+        <v>-0.2865</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9320000000000001</v>
+        <v>3.2684</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3316</v>
+        <v>5.0732</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5673</v>
+        <v>3.8847</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7643</v>
+        <v>1.1885</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1027</v>
+        <v>2.3703</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2742</v>
+        <v>1.9068</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8285</v>
+        <v>0.4635</v>
       </c>
       <c r="J3" t="n">
-        <v>3.722</v>
+        <v>4.0289</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4809</v>
+        <v>1.5341</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2411</v>
+        <v>2.4949</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6193</v>
+        <v>-1.6587</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2066</v>
+        <v>0.3727</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4126</v>
+        <v>-2.0314</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5028</v>
+        <v>0.1778</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9376</v>
+        <v>0.1321</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5653</v>
+        <v>0.0457</v>
       </c>
       <c r="V3" t="n">
-        <v>3.278</v>
+        <v>0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>3.278</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>M. PANTZAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1217</v>
+        <v>4.379</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0777</v>
+        <v>3.0557</v>
       </c>
       <c r="F4" t="n">
-        <v>1.044</v>
+        <v>1.3233</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2447</v>
+        <v>2.9101</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0896</v>
+        <v>0.9392</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8449</v>
+        <v>1.9709</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3445</v>
+        <v>4.4686</v>
       </c>
       <c r="K4" t="n">
-        <v>3.934</v>
+        <v>0.7822</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4105</v>
+        <v>3.6864</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0998</v>
+        <v>-1.5585</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1556</v>
+        <v>0.157</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2554</v>
+        <v>-1.7155</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4025</v>
+        <v>2.9592</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6728</v>
+        <v>-0.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8389</v>
+        <v>-0.3627</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1661</v>
+        <v>-0.0774</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7032</v>
+        <v>0.3155</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6105</v>
+        <v>0.3155</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PANTZAR</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0558</v>
+        <v>3.9035</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5502</v>
+        <v>2.1454</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5056</v>
+        <v>1.7582</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9066</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9394</v>
+        <v>1.9585</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9672</v>
+        <v>-2.0261</v>
       </c>
       <c r="J5" t="n">
-        <v>4.494</v>
+        <v>1.4764</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7997</v>
+        <v>1.3133</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6944</v>
+        <v>0.1632</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5875</v>
+        <v>-1.5441</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1397</v>
+        <v>0.6452</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7272</v>
+        <v>-2.1893</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9488</v>
+        <v>3.6421</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7601</v>
+        <v>-0.663</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9043</v>
+        <v>-0.3232</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1442</v>
+        <v>-0.3399</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3214</v>
+        <v>3.2684</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3214</v>
+        <v>3.2684</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2695</v>
+        <v>2.8609</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7674</v>
+        <v>1.8067</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5021</v>
+        <v>1.0543</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0668</v>
+        <v>3.2414</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9537</v>
+        <v>4.0735</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0205</v>
+        <v>-0.8321</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5047</v>
+        <v>4.3116</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3263</v>
+        <v>3.902</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1785</v>
+        <v>0.4096</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5716</v>
+        <v>-1.0703</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6274</v>
+        <v>0.1715</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.199</v>
+        <v>-1.2417</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6293</v>
+        <v>3.4145</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3026</v>
+        <v>0.4147</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.747</v>
+        <v>0.6151</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5556</v>
+        <v>-0.2005</v>
       </c>
       <c r="V6" t="n">
-        <v>3.278</v>
+        <v>-1.7057</v>
       </c>
       <c r="W6" t="n">
-        <v>3.278</v>
+        <v>-0.6162</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9174</v>
+        <v>1.2469</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7721</v>
+        <v>2.012</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8546</v>
+        <v>-0.7651</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6024</v>
+        <v>1.6069</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6189</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9835</v>
+        <v>0.9785</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3104</v>
+        <v>2.2932</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3753</v>
+        <v>1.3624</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.708</v>
+        <v>-0.6863</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9533</v>
+        <v>-0.6363</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5383</v>
+        <v>-0.2812</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.415</v>
+        <v>-0.3551</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8269</v>
+        <v>0.8242</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1192</v>
+        <v>-0.0192</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.8434</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6849</v>
+        <v>0.6826</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1601</v>
+        <v>-0.1635</v>
       </c>
       <c r="I8" t="n">
-        <v>0.845</v>
+        <v>0.8462</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2038</v>
+        <v>1.1821</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1243</v>
+        <v>0.1099</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5189</v>
+        <v>-0.4995</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5916</v>
+        <v>-0.5805</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2419</v>
+        <v>-0.1024</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3496</v>
+        <v>-0.4782</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5397</v>
+        <v>-1.4142</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0173</v>
+        <v>0.1357</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.557</v>
+        <v>-1.5499</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1986</v>
+        <v>-0.1972</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1746</v>
+        <v>0.1752</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,22 +1156,22 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0877</v>
+        <v>0.0302</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.1184</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0877</v>
+        <v>-0.0882</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9029</v>
+        <v>-3.347</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1762</v>
+        <v>-1.6612</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7267</v>
+        <v>-1.6858</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8492</v>
+        <v>-0.8545</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0043</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.845</v>
+        <v>-0.8462</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7588</v>
+        <v>-0.7692</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0275</v>
+        <v>0.0205</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0854</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4927</v>
+        <v>0.0523</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7168</v>
+        <v>0.2462</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2241</v>
+        <v>-0.1939</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6279</v>
+        <v>-3.4528</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7368</v>
+        <v>-0.5558</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8912</v>
+        <v>-2.897</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4697</v>
+        <v>-1.4611</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4948</v>
+        <v>0.5022</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9645</v>
+        <v>-1.9633</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1803</v>
+        <v>-0.1864</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2894</v>
+        <v>-1.2747</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7195</v>
+        <v>-0.5655</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5565</v>
+        <v>-0.3695</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.163</v>
+        <v>-0.1961</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1991</v>
+        <v>-3.7504</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7312</v>
+        <v>-1.4046</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4678</v>
+        <v>-2.3458</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6972</v>
+        <v>-0.6993</v>
       </c>
       <c r="H12" t="n">
-        <v>0.417</v>
+        <v>0.4165</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1142</v>
+        <v>-1.1158</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8667</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6856</v>
+        <v>0.6755</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1812</v>
+        <v>0.1708</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5639</v>
+        <v>-1.5457</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4092</v>
+        <v>0.0384</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3297</v>
+        <v>0.0253</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0796</v>
+        <v>0.013</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.7107</v>
+        <v>11.4112</v>
       </c>
       <c r="E13" t="n">
-        <v>13.0097</v>
+        <v>13.402</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.298900000000001</v>
+        <v>-1.9906</v>
       </c>
       <c r="G13" t="n">
-        <v>9.620000000000001</v>
+        <v>9.6264</v>
       </c>
       <c r="H13" t="n">
-        <v>10.6995</v>
+        <v>10.6987</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0796</v>
+        <v>-1.0722</v>
       </c>
       <c r="J13" t="n">
-        <v>21.5657</v>
+        <v>21.3509</v>
       </c>
       <c r="K13" t="n">
-        <v>10.478</v>
+        <v>10.3467</v>
       </c>
       <c r="L13" t="n">
-        <v>11.0879</v>
+        <v>11.0046</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.9459</v>
+        <v>-11.725</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2216999999999999</v>
+        <v>0.3519</v>
       </c>
       <c r="O13" t="n">
-        <v>-12.1675</v>
+        <v>-12.0767</v>
       </c>
       <c r="P13" t="n">
-        <v>5.6708</v>
+        <v>5.690799999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.8784</v>
+        <v>-15.9341</v>
       </c>
       <c r="R13" t="n">
-        <v>21.549</v>
+        <v>21.625</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.5839</v>
+        <v>-2.9024</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4516</v>
+        <v>-0.7460000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.1325</v>
+        <v>-2.1571</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9962000000000009</v>
+        <v>-1.003199999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>8.7737</v>
+        <v>8.730600000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.7699</v>
+        <v>-9.7338</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6048</v>
+        <v>5.4157</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1194</v>
+        <v>5.2148</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4854</v>
+        <v>0.2009</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0135</v>
+        <v>1.0173</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8413</v>
+        <v>-1.8383</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8548</v>
+        <v>2.8556</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9128</v>
+        <v>2.8945</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7069</v>
+        <v>-0.7174</v>
       </c>
       <c r="L14" t="n">
-        <v>3.6197</v>
+        <v>3.612</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8993</v>
+        <v>-1.8772</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0449</v>
+        <v>0.8536</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0212</v>
+        <v>0.1414</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0238</v>
+        <v>0.7123</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6152</v>
+        <v>1.1708</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2842</v>
+        <v>3.189</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.669</v>
+        <v>-2.0183</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0327</v>
+        <v>2.481</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.1629</v>
+        <v>1.9301</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1302</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5384</v>
+        <v>5.0464</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8871</v>
+        <v>3.0509</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4256</v>
+        <v>1.9955</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5711</v>
+        <v>-2.5654</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2758</v>
+        <v>-1.1209</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2954</v>
+        <v>-1.4446</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0415</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.6293</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2791</v>
+        <v>0.5517</v>
       </c>
       <c r="T15" t="n">
-        <v>3.0971</v>
+        <v>0.1019</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1821</v>
+        <v>0.4498</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4102</v>
+        <v>-1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>3.278</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8678</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8387</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>2.518</v>
+        <v>0.6122</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6793</v>
+        <v>0.3621</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4877</v>
+        <v>-1.1562</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9307</v>
+        <v>-0.8763</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5570000000000001</v>
+        <v>-0.2799</v>
       </c>
       <c r="J16" t="n">
-        <v>5.0748</v>
+        <v>-0.296</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0651</v>
+        <v>-0.4449</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0097</v>
+        <v>0.1489</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.587</v>
+        <v>-0.8603</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1344</v>
+        <v>-0.4314</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4526</v>
+        <v>-0.4289</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2168</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6079</v>
+        <v>-0.1813</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8247</v>
+        <v>0.1721</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.639</v>
+        <v>0.7739</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1853</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5657</v>
+        <v>0.3051</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3845</v>
+        <v>2.0042</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1812</v>
+        <v>-1.6991</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1643</v>
+        <v>-1.0344</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8817</v>
+        <v>-2.1681</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2825</v>
+        <v>1.1338</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2908</v>
+        <v>1.5166</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.44</v>
+        <v>-0.9038</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>2.4204</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-2.551</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4417</v>
+        <v>-1.2643</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4318</v>
+        <v>-1.2866</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4023</v>
+        <v>0.98</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4174</v>
+        <v>0.8613</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0151</v>
+        <v>0.1187</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7712</v>
+        <v>2.4082</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>3.2684</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0179</v>
+        <v>-0.0497</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5618</v>
+        <v>1.3226</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5438</v>
+        <v>-1.3723</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2025</v>
+        <v>-0.1957</v>
       </c>
       <c r="H18" t="n">
-        <v>0.176</v>
+        <v>0.178</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3785</v>
+        <v>-0.3737</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6661</v>
+        <v>0.6633</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5541</v>
+        <v>0.5516</v>
       </c>
       <c r="L18" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8685</v>
+        <v>-0.859</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9255</v>
+        <v>0.8501</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7349</v>
+        <v>0.5016</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1905</v>
+        <v>0.3485</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,22 +1891,22 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8537</v>
+        <v>-0.8187</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7145</v>
+        <v>-0.6793</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4209</v>
+        <v>-0.4157</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1918,13 +1918,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4209</v>
+        <v>-0.4157</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4328</v>
+        <v>-0.403</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2937</v>
+        <v>-0.2636</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4102</v>
+        <v>-0.9896</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0669</v>
+        <v>0.0433</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3433</v>
+        <v>-1.0329</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.891</v>
+        <v>-2.878</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6596</v>
+        <v>-1.6491</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2315</v>
+        <v>-1.2288</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0881</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5944</v>
+        <v>0.5881</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8029</v>
+        <v>-2.7799</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1071</v>
+        <v>0.2949</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0212</v>
+        <v>0.1414</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1282</v>
+        <v>0.1535</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0171</v>
+        <v>-1.0202</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0253</v>
+        <v>-0.4624</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9918</v>
+        <v>-0.5579</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7005</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8051</v>
+        <v>0.8097</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5056</v>
+        <v>-2.5102</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7133</v>
+        <v>0.6925</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7663</v>
+        <v>1.7582</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.053</v>
+        <v>-1.0656</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4139</v>
+        <v>-2.3931</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9308999999999999</v>
+        <v>0.0673</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5383</v>
+        <v>0.0531</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3926</v>
+        <v>0.0141</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5216</v>
+        <v>-2.7607</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7209</v>
+        <v>-2.5397</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1993</v>
+        <v>-0.221</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6593</v>
+        <v>-3.7989</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9738</v>
+        <v>-1.1949</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3145</v>
+        <v>-2.604</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.154</v>
+        <v>-2.3374</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2335</v>
+        <v>-0.1174</v>
       </c>
       <c r="L22" t="n">
-        <v>1.0795</v>
+        <v>-2.22</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5053</v>
+        <v>-1.4615</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-1.0775</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7649</v>
+        <v>-0.384</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.1757</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2207</v>
+        <v>0.3553</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8771</v>
+        <v>0.0253</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3436</v>
+        <v>0.33</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5265</v>
+        <v>-2.8455</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8773</v>
+        <v>-3.3495</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6492</v>
+        <v>0.504</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.7993</v>
+        <v>-1.6655</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1977</v>
+        <v>-1.9813</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6016</v>
+        <v>0.3159</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3208</v>
+        <v>-0.1763</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.111</v>
+        <v>-1.2485</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2098</v>
+        <v>1.0722</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4785</v>
+        <v>-1.4891</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0867</v>
+        <v>-0.7328</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3918</v>
+        <v>-0.7563</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6805</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-4.5526</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4077</v>
+        <v>0.9173</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3297</v>
+        <v>0.29</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.078</v>
+        <v>0.6273</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9235</v>
+        <v>-3.9878</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6147</v>
+        <v>-1.9673</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3088</v>
+        <v>-2.0205</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0338</v>
+        <v>-0.0542</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3474</v>
+        <v>-2.3629</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3136</v>
+        <v>2.3087</v>
       </c>
       <c r="J24" t="n">
-        <v>2.5264</v>
+        <v>2.4836</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8667</v>
+        <v>-0.8973</v>
       </c>
       <c r="L24" t="n">
-        <v>3.3931</v>
+        <v>3.3809</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5602</v>
+        <v>-2.5378</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4807</v>
+        <v>-1.4656</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6875</v>
+        <v>0.2728</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5383</v>
+        <v>0.1716</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1491</v>
+        <v>0.1013</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1005</v>
+        <v>-4.5286</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1247</v>
+        <v>-1.9373</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9758</v>
+        <v>-2.5913</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2171</v>
+        <v>-0.2256</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4992</v>
+        <v>-1.5019</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2821</v>
+        <v>1.2763</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3677</v>
+        <v>1.3357</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6793</v>
+        <v>-0.697</v>
       </c>
       <c r="L25" t="n">
-        <v>2.047</v>
+        <v>2.0327</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5848</v>
+        <v>-1.5613</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1349</v>
+        <v>0.4482</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0484</v>
+        <v>0.1901</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.2581</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.7108</v>
+        <v>-9.134899999999998</v>
       </c>
       <c r="E26" t="n">
-        <v>2.299000000000001</v>
+        <v>1.990500000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-13.0096</v>
+        <v>-11.1256</v>
       </c>
       <c r="G26" t="n">
-        <v>-9.620200000000001</v>
+        <v>-9.6264</v>
       </c>
       <c r="H26" t="n">
-        <v>-10.6995</v>
+        <v>-10.6983</v>
       </c>
       <c r="I26" t="n">
-        <v>1.079300000000001</v>
+        <v>1.0722</v>
       </c>
       <c r="J26" t="n">
-        <v>11.9458</v>
+        <v>11.7248</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2214999999999996</v>
+        <v>-0.3517999999999998</v>
       </c>
       <c r="L26" t="n">
-        <v>12.1675</v>
+        <v>12.0768</v>
       </c>
       <c r="M26" t="n">
-        <v>-21.5659</v>
+        <v>-21.3513</v>
       </c>
       <c r="N26" t="n">
-        <v>-10.478</v>
+        <v>-10.3467</v>
       </c>
       <c r="O26" t="n">
-        <v>-11.0878</v>
+        <v>-11.0045</v>
       </c>
       <c r="P26" t="n">
-        <v>-5.6708</v>
+        <v>-5.690700000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-21.5492</v>
+        <v>-21.6249</v>
       </c>
       <c r="R26" t="n">
-        <v>15.8782</v>
+        <v>15.9342</v>
       </c>
       <c r="S26" t="n">
-        <v>3.583799999999999</v>
+        <v>5.178900000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1324</v>
+        <v>2.157</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4517</v>
+        <v>3.0221</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9959999999999991</v>
+        <v>1.003199999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>9.769800000000002</v>
+        <v>9.733899999999998</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.7737</v>
+        <v>-8.730600000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104651_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104651_W22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-9.7338</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104651_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-8.730600000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
